--- a/templates/template_input3.xlsx
+++ b/templates/template_input3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -475,14 +475,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>· 근무 희망: D / E / N / 8A / NK / T(교육)</t>
+          <t>· 근무 희망: D / E / N / 8A / 9A / NK / T(교육) / TW(반근무+반교육)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>· 휴가유형별 희망: 연·연차(연차) / 연4(반차) / 조(조사) / 경(경조사) / 공(공가) / 병(병가) / 휴(휴직) / 승(승급교육)</t>
+          <t>· 휴가유형별 희망: 연·연차(연차) / 연1·연2·연3(시간제 연차) / 연4(반차) / 조(조사) / 경(경조사) / 공(공가) / 병(병가) / 휴(휴직) / 승(승급교육) / 군(군공가) / S/(수면오프)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>· 그 외 인식 못 하는 표시(포상휴가·군휴가 등 특수 코드)는 업로드 후 '인식 못 한 표시' 목록으로 알려드립니다.</t>
+          <t>· 그 외 인식 못 하는 표시(포상휴가 등 특수 코드)는 업로드 후 '인식 못 한 표시' 목록으로 알려드립니다.</t>
         </is>
       </c>
     </row>
@@ -541,22 +541,41 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>· 연4(반차): 0.5일 연차 + 0.5일 휴무로 집계됩니다</t>
+          <t>· 연1/연2/연3/연4(시간제/반차 연차): 몇 시간이든 하루치 연차 희망으로 집계됩니다</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>· 군(군공가)/S/(수면오프): 휴무(OFF)와 동일하게 취급되지만 잔휴에는 반영되지 않습니다</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>가장 쉬운 사용법</t>
+          <t>· TW(반근무+반교육): 근무일수엔 포함되지만 최소인력 계산에는 제외됩니다(교육 T와 동일)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>· 9A(09시 시작): 8A와 동격으로 취급됩니다(시작 시각만 다름)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>가장 쉬운 사용법</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>이번 달 근무표를 아무 값이나 넣어 한 번 생성해서 빈 그리드 모양(입력②와 같은 모양)을 받은 뒤, 그 위에 표시만 채워서 다시 올려도 됩니다.</t>
         </is>
